--- a/tame_output/ON/bt/strategyON_20240526.xlsx
+++ b/tame_output/ON/bt/strategyON_20240526.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.4%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -773,11 +773,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-30.1%</t>
+          <t>-30.2%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.3%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-623.6%</t>
+          <t>-623.5%</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.5%</t>
+          <t>-38.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-279.5%</t>
+          <t>-279.6%</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-137.2%</t>
+          <t>-137.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-177.7%</t>
+          <t>-177.8%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1974"/>
+  <dimension ref="A1:G1975"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831231332909034</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
@@ -46963,6 +46963,29 @@
       </c>
       <c r="G1974" t="n">
         <v>2.683410693378864</v>
+      </c>
+    </row>
+    <row r="1975">
+      <c r="A1975" s="2" t="n">
+        <v>45437</v>
+      </c>
+      <c r="B1975" t="n">
+        <v>3.834464403548158</v>
+      </c>
+      <c r="C1975" t="n">
+        <v>2.813896405829816</v>
+      </c>
+      <c r="D1975" t="n">
+        <v>-4.619190431639999</v>
+      </c>
+      <c r="E1975" t="n">
+        <v>0.9658638088600688</v>
+      </c>
+      <c r="F1975" t="n">
+        <v>-0.219990157351706</v>
+      </c>
+      <c r="G1975" t="n">
+        <v>2.681902311418793</v>
       </c>
     </row>
   </sheetData>
